--- a/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 04/XKBH_MinhKhang_010426.xlsx
+++ b/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 04/XKBH_MinhKhang_010426.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\2. Bảo hành\Xuất nhập kho 2026\Xuất kho\Tháng 04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DD4C89-CCBB-483B-9455-8A08C4072397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35849D11-A928-40A7-A079-6CCDA3742112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,9 +102,6 @@
     <t>Tổng</t>
   </si>
   <si>
-    <t xml:space="preserve">Tên Khách hàng: </t>
-  </si>
-  <si>
     <t>Hà Nội, ngày 01 tháng 04 năm 2026</t>
   </si>
   <si>
@@ -123,6 +120,9 @@
   </si>
   <si>
     <t>VT_Module_A7677S (A7677 Z3283)</t>
+  </si>
+  <si>
+    <t>Tên Khách hàng: Đai lý Minh Khang</t>
   </si>
 </sst>
 </file>
@@ -468,6 +468,36 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,36 +554,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -978,70 +978,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="37"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="47"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="38" t="s">
+      <c r="A2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="49"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="38" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="40" t="s">
+      <c r="A4" s="42"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="51"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="25"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
@@ -1050,7 +1050,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1067,7 +1067,7 @@
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
@@ -1108,10 +1108,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="20">
         <v>2</v>
@@ -1124,20 +1124,20 @@
         <v>400000</v>
       </c>
       <c r="G10" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="20" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="22">
         <f>SUM(F10:F10)</f>
         <v>400000</v>
@@ -1156,40 +1156,40 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="44" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44" t="s">
+      <c r="D13" s="25"/>
+      <c r="E13" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="44"/>
-      <c r="G13" s="46" t="s">
+      <c r="F13" s="25"/>
+      <c r="G13" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="46"/>
+      <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="49" t="s">
+      <c r="B14" s="29"/>
+      <c r="C14" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="50" t="s">
+      <c r="D14" s="30"/>
+      <c r="E14" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51" t="s">
+      <c r="F14" s="31"/>
+      <c r="G14" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="51"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
@@ -1242,22 +1242,22 @@
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44" t="s">
+      <c r="B20" s="24"/>
+      <c r="C20" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="45" t="s">
+      <c r="D20" s="25"/>
+      <c r="E20" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46" t="s">
+      <c r="F20" s="26"/>
+      <c r="G20" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="46"/>
+      <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1283,6 +1283,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C20:D20"/>
@@ -1296,12 +1302,6 @@
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
